--- a/12603996.xlsx
+++ b/12603996.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://lpuin-my.sharepoint.com/personal/shubham_bither2026_lpu_in/Documents/CAP776/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="375" documentId="8_{04F8DF2E-49C5-3B44-B164-C4F738DF63B4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{CE09EABE-76A7-4171-904F-1E909C6481DD}"/>
+  <xr:revisionPtr revIDLastSave="442" documentId="8_{04F8DF2E-49C5-3B44-B164-C4F738DF63B4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{C649ECD3-B54A-495A-92F5-D1F662572D09}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13176" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="169" uniqueCount="93">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="189" uniqueCount="99">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -314,6 +314,24 @@
   </si>
   <si>
     <t>started studying late due to headache</t>
+  </si>
+  <si>
+    <t>today I ride at 60/70 kmph , didn’t push 80 today</t>
+  </si>
+  <si>
+    <t>due to bike problem less time was dedicated to study</t>
+  </si>
+  <si>
+    <t>today python ca was conducted</t>
+  </si>
+  <si>
+    <t>not able to study due to disorganised sleep cycle</t>
+  </si>
+  <si>
+    <t>low</t>
+  </si>
+  <si>
+    <t>not able to study due to disorganised sleep cycle &amp; other chores</t>
   </si>
 </sst>
 </file>
@@ -2430,132 +2448,256 @@
         <v>92</v>
       </c>
     </row>
-    <row r="35" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A35" s="13"/>
-      <c r="B35" s="14"/>
-      <c r="C35" s="14"/>
-      <c r="D35" s="14"/>
-      <c r="E35" s="14"/>
-      <c r="F35" s="14"/>
-      <c r="G35" s="14"/>
-      <c r="H35" s="14"/>
-      <c r="I35" s="15" t="str">
+    <row r="35" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A35" s="13">
+        <v>46278</v>
+      </c>
+      <c r="B35" s="14">
+        <v>600</v>
+      </c>
+      <c r="C35" s="14">
+        <v>100</v>
+      </c>
+      <c r="D35" s="14">
+        <v>0</v>
+      </c>
+      <c r="E35" s="14">
+        <v>0</v>
+      </c>
+      <c r="F35" s="14">
+        <v>0</v>
+      </c>
+      <c r="G35" s="14">
+        <v>0</v>
+      </c>
+      <c r="H35" s="14">
+        <v>630</v>
+      </c>
+      <c r="I35" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J35" s="15" t="str">
+        <v>1330</v>
+      </c>
+      <c r="J35" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K35" s="16"/>
-      <c r="L35" s="16"/>
-      <c r="M35" s="16"/>
-      <c r="N35" s="17"/>
-    </row>
-    <row r="36" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A36" s="13"/>
-      <c r="B36" s="14"/>
-      <c r="C36" s="14"/>
-      <c r="D36" s="14"/>
-      <c r="E36" s="14"/>
-      <c r="F36" s="14"/>
-      <c r="G36" s="14"/>
-      <c r="H36" s="14"/>
-      <c r="I36" s="15" t="str">
+        <v>110</v>
+      </c>
+      <c r="K35" s="16" t="s">
+        <v>64</v>
+      </c>
+      <c r="L35" s="16" t="s">
+        <v>62</v>
+      </c>
+      <c r="M35" s="16" t="s">
+        <v>64</v>
+      </c>
+      <c r="N35" s="17" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="36" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A36" s="13">
+        <v>46279</v>
+      </c>
+      <c r="B36" s="14">
+        <v>240</v>
+      </c>
+      <c r="C36" s="14">
+        <v>80</v>
+      </c>
+      <c r="D36" s="14">
+        <v>32</v>
+      </c>
+      <c r="E36" s="14">
+        <v>103</v>
+      </c>
+      <c r="F36" s="14">
+        <v>100</v>
+      </c>
+      <c r="G36" s="14">
+        <v>2</v>
+      </c>
+      <c r="H36" s="14">
+        <v>520</v>
+      </c>
+      <c r="I36" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J36" s="15" t="str">
+        <v>1075</v>
+      </c>
+      <c r="J36" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K36" s="16"/>
-      <c r="L36" s="16"/>
-      <c r="M36" s="16"/>
-      <c r="N36" s="17"/>
+        <v>365</v>
+      </c>
+      <c r="K36" s="16" t="s">
+        <v>64</v>
+      </c>
+      <c r="L36" s="16" t="s">
+        <v>61</v>
+      </c>
+      <c r="M36" s="16" t="s">
+        <v>51</v>
+      </c>
+      <c r="N36" s="17" t="s">
+        <v>94</v>
+      </c>
     </row>
     <row r="37" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A37" s="13"/>
-      <c r="B37" s="14"/>
-      <c r="C37" s="14"/>
-      <c r="D37" s="14"/>
-      <c r="E37" s="14"/>
-      <c r="F37" s="14"/>
-      <c r="G37" s="14"/>
-      <c r="H37" s="14"/>
-      <c r="I37" s="15" t="str">
+      <c r="A37" s="13">
+        <v>46280</v>
+      </c>
+      <c r="B37" s="14">
+        <v>270</v>
+      </c>
+      <c r="C37" s="14">
+        <v>80</v>
+      </c>
+      <c r="D37" s="14">
+        <v>45</v>
+      </c>
+      <c r="E37" s="14">
+        <v>90</v>
+      </c>
+      <c r="F37" s="14">
+        <v>250</v>
+      </c>
+      <c r="G37" s="14">
+        <v>5</v>
+      </c>
+      <c r="H37" s="14">
+        <v>320</v>
+      </c>
+      <c r="I37" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J37" s="15" t="str">
+        <v>1055</v>
+      </c>
+      <c r="J37" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K37" s="16"/>
-      <c r="L37" s="16"/>
-      <c r="M37" s="16"/>
-      <c r="N37" s="17"/>
-    </row>
-    <row r="38" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A38" s="13"/>
-      <c r="B38" s="14"/>
-      <c r="C38" s="14"/>
-      <c r="D38" s="14"/>
-      <c r="E38" s="14"/>
-      <c r="F38" s="14"/>
-      <c r="G38" s="14"/>
-      <c r="H38" s="14"/>
-      <c r="I38" s="15" t="str">
+        <v>385</v>
+      </c>
+      <c r="K37" s="16" t="s">
+        <v>67</v>
+      </c>
+      <c r="L37" s="16" t="s">
+        <v>62</v>
+      </c>
+      <c r="M37" s="16" t="s">
+        <v>51</v>
+      </c>
+      <c r="N37" s="17" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="38" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A38" s="13">
+        <v>46281</v>
+      </c>
+      <c r="B38" s="14">
+        <v>287</v>
+      </c>
+      <c r="C38" s="14">
+        <v>140</v>
+      </c>
+      <c r="D38" s="14">
+        <v>0</v>
+      </c>
+      <c r="E38" s="14">
+        <v>0</v>
+      </c>
+      <c r="F38" s="14">
+        <v>150</v>
+      </c>
+      <c r="G38" s="14">
+        <v>3</v>
+      </c>
+      <c r="H38" s="14">
+        <v>523</v>
+      </c>
+      <c r="I38" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J38" s="15" t="str">
+        <v>1100</v>
+      </c>
+      <c r="J38" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K38" s="16"/>
-      <c r="L38" s="16"/>
-      <c r="M38" s="16"/>
-      <c r="N38" s="17"/>
-    </row>
-    <row r="39" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A39" s="13"/>
-      <c r="B39" s="14"/>
-      <c r="C39" s="14"/>
-      <c r="D39" s="14"/>
-      <c r="E39" s="14"/>
-      <c r="F39" s="14"/>
-      <c r="G39" s="14"/>
-      <c r="H39" s="14"/>
-      <c r="I39" s="15" t="str">
+        <v>340</v>
+      </c>
+      <c r="K38" s="16" t="s">
+        <v>67</v>
+      </c>
+      <c r="L38" s="16" t="s">
+        <v>68</v>
+      </c>
+      <c r="M38" s="16" t="s">
+        <v>64</v>
+      </c>
+      <c r="N38" s="17" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="39" spans="1:14" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A39" s="13">
+        <v>46282</v>
+      </c>
+      <c r="B39" s="14">
+        <v>285</v>
+      </c>
+      <c r="C39" s="14">
+        <v>160</v>
+      </c>
+      <c r="D39" s="14">
+        <v>47</v>
+      </c>
+      <c r="E39" s="14">
+        <v>0</v>
+      </c>
+      <c r="F39" s="14">
+        <v>350</v>
+      </c>
+      <c r="G39" s="14">
+        <v>7</v>
+      </c>
+      <c r="H39" s="14">
+        <v>429</v>
+      </c>
+      <c r="I39" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J39" s="15" t="str">
+        <v>1271</v>
+      </c>
+      <c r="J39" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K39" s="16"/>
-      <c r="L39" s="16"/>
-      <c r="M39" s="16"/>
-      <c r="N39" s="17"/>
+        <v>169</v>
+      </c>
+      <c r="K39" s="16" t="s">
+        <v>67</v>
+      </c>
+      <c r="L39" s="16" t="s">
+        <v>68</v>
+      </c>
+      <c r="M39" s="16" t="s">
+        <v>97</v>
+      </c>
+      <c r="N39" s="17" t="s">
+        <v>98</v>
+      </c>
     </row>
     <row r="40" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A40" s="13"/>
-      <c r="B40" s="14"/>
+      <c r="A40" s="13">
+        <v>46283</v>
+      </c>
+      <c r="B40" s="14">
+        <v>287</v>
+      </c>
       <c r="C40" s="14"/>
       <c r="D40" s="14"/>
       <c r="E40" s="14"/>
       <c r="F40" s="14"/>
       <c r="G40" s="14"/>
       <c r="H40" s="14"/>
-      <c r="I40" s="15" t="str">
+      <c r="I40" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J40" s="15" t="str">
+        <v>287</v>
+      </c>
+      <c r="J40" s="15">
         <f t="shared" si="1"/>
-        <v/>
+        <v>1153</v>
       </c>
       <c r="K40" s="16"/>
       <c r="L40" s="16"/>

--- a/12603996.xlsx
+++ b/12603996.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://lpuin-my.sharepoint.com/personal/shubham_bither2026_lpu_in/Documents/CAP776/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="442" documentId="8_{04F8DF2E-49C5-3B44-B164-C4F738DF63B4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{C649ECD3-B54A-495A-92F5-D1F662572D09}"/>
+  <xr:revisionPtr revIDLastSave="466" documentId="8_{04F8DF2E-49C5-3B44-B164-C4F738DF63B4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{3BA5452D-F997-4E31-B2C7-C13DBBDE337F}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13176" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-23148" yWindow="-108" windowWidth="23256" windowHeight="13176" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Instructions" sheetId="1" r:id="rId1"/>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="189" uniqueCount="99">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="197" uniqueCount="101">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -332,6 +332,12 @@
   </si>
   <si>
     <t>not able to study due to disorganised sleep cycle &amp; other chores</t>
+  </si>
+  <si>
+    <t>my performance in maths ca was very bad</t>
+  </si>
+  <si>
+    <t>studied for math ca</t>
   </si>
 </sst>
 </file>
@@ -2685,46 +2691,88 @@
       <c r="B40" s="14">
         <v>287</v>
       </c>
-      <c r="C40" s="14"/>
-      <c r="D40" s="14"/>
-      <c r="E40" s="14"/>
-      <c r="F40" s="14"/>
-      <c r="G40" s="14"/>
-      <c r="H40" s="14"/>
+      <c r="C40" s="14">
+        <v>160</v>
+      </c>
+      <c r="D40" s="14">
+        <v>150</v>
+      </c>
+      <c r="E40" s="14">
+        <v>0</v>
+      </c>
+      <c r="F40" s="14">
+        <v>300</v>
+      </c>
+      <c r="G40" s="14">
+        <v>6</v>
+      </c>
+      <c r="H40" s="14">
+        <v>485</v>
+      </c>
       <c r="I40" s="15">
         <f t="shared" si="0"/>
-        <v>287</v>
+        <v>1382</v>
       </c>
       <c r="J40" s="15">
         <f t="shared" si="1"/>
-        <v>1153</v>
-      </c>
-      <c r="K40" s="16"/>
-      <c r="L40" s="16"/>
-      <c r="M40" s="16"/>
-      <c r="N40" s="17"/>
-    </row>
-    <row r="41" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A41" s="13"/>
-      <c r="B41" s="14"/>
-      <c r="C41" s="14"/>
-      <c r="D41" s="14"/>
-      <c r="E41" s="14"/>
-      <c r="F41" s="14"/>
+        <v>58</v>
+      </c>
+      <c r="K40" s="16" t="s">
+        <v>61</v>
+      </c>
+      <c r="L40" s="16" t="s">
+        <v>68</v>
+      </c>
+      <c r="M40" s="16" t="s">
+        <v>64</v>
+      </c>
+      <c r="N40" s="17" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="41" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A41" s="13">
+        <v>46284</v>
+      </c>
+      <c r="B41" s="14">
+        <v>327</v>
+      </c>
+      <c r="C41" s="14">
+        <v>100</v>
+      </c>
+      <c r="D41" s="14">
+        <v>150</v>
+      </c>
+      <c r="E41" s="14">
+        <v>0</v>
+      </c>
+      <c r="F41" s="14">
+        <v>0</v>
+      </c>
       <c r="G41" s="14"/>
-      <c r="H41" s="14"/>
-      <c r="I41" s="15" t="str">
+      <c r="H41" s="14">
+        <v>483</v>
+      </c>
+      <c r="I41" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J41" s="15" t="str">
+        <v>1060</v>
+      </c>
+      <c r="J41" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K41" s="16"/>
-      <c r="L41" s="16"/>
-      <c r="M41" s="16"/>
-      <c r="N41" s="17"/>
+        <v>380</v>
+      </c>
+      <c r="K41" s="16" t="s">
+        <v>61</v>
+      </c>
+      <c r="L41" s="16" t="s">
+        <v>62</v>
+      </c>
+      <c r="M41" s="16" t="s">
+        <v>64</v>
+      </c>
+      <c r="N41" s="17" t="s">
+        <v>99</v>
+      </c>
     </row>
     <row r="42" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A42" s="13"/>

--- a/12603996.xlsx
+++ b/12603996.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://lpuin-my.sharepoint.com/personal/shubham_bither2026_lpu_in/Documents/CAP776/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="466" documentId="8_{04F8DF2E-49C5-3B44-B164-C4F738DF63B4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{3BA5452D-F997-4E31-B2C7-C13DBBDE337F}"/>
+  <xr:revisionPtr revIDLastSave="495" documentId="8_{04F8DF2E-49C5-3B44-B164-C4F738DF63B4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{81B4A34B-44D8-497D-B70E-2B67997CF4CC}"/>
   <bookViews>
-    <workbookView xWindow="-23148" yWindow="-108" windowWidth="23256" windowHeight="13176" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13176" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Instructions" sheetId="1" r:id="rId1"/>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="197" uniqueCount="101">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="205" uniqueCount="103">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -338,6 +338,12 @@
   </si>
   <si>
     <t>studied for math ca</t>
+  </si>
+  <si>
+    <t>made logic for python mini project</t>
+  </si>
+  <si>
+    <t>due to my medicine finished , energy level has decreased in body which is effecting my productivity</t>
   </si>
 </sst>
 </file>
@@ -2749,7 +2755,9 @@
       <c r="F41" s="14">
         <v>0</v>
       </c>
-      <c r="G41" s="14"/>
+      <c r="G41" s="14">
+        <v>0</v>
+      </c>
       <c r="H41" s="14">
         <v>483</v>
       </c>
@@ -2774,49 +2782,97 @@
         <v>99</v>
       </c>
     </row>
-    <row r="42" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A42" s="13"/>
-      <c r="B42" s="14"/>
-      <c r="C42" s="14"/>
-      <c r="D42" s="14"/>
-      <c r="E42" s="14"/>
-      <c r="F42" s="14"/>
-      <c r="G42" s="14"/>
-      <c r="H42" s="14"/>
-      <c r="I42" s="15" t="str">
+    <row r="42" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A42" s="13">
+        <v>46285</v>
+      </c>
+      <c r="B42" s="14">
+        <v>520</v>
+      </c>
+      <c r="C42" s="14">
+        <v>0</v>
+      </c>
+      <c r="D42" s="14">
+        <v>93</v>
+      </c>
+      <c r="E42" s="14">
+        <v>204</v>
+      </c>
+      <c r="F42" s="14">
+        <v>0</v>
+      </c>
+      <c r="G42" s="14">
+        <v>0</v>
+      </c>
+      <c r="H42" s="14">
+        <v>543</v>
+      </c>
+      <c r="I42" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J42" s="15" t="str">
+        <v>1360</v>
+      </c>
+      <c r="J42" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K42" s="16"/>
-      <c r="L42" s="16"/>
-      <c r="M42" s="16"/>
-      <c r="N42" s="17"/>
-    </row>
-    <row r="43" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A43" s="13"/>
-      <c r="B43" s="14"/>
-      <c r="C43" s="14"/>
-      <c r="D43" s="14"/>
-      <c r="E43" s="14"/>
-      <c r="F43" s="14"/>
-      <c r="G43" s="14"/>
-      <c r="H43" s="14"/>
-      <c r="I43" s="15" t="str">
+        <v>80</v>
+      </c>
+      <c r="K42" s="16" t="s">
+        <v>61</v>
+      </c>
+      <c r="L42" s="16" t="s">
+        <v>61</v>
+      </c>
+      <c r="M42" s="16" t="s">
+        <v>51</v>
+      </c>
+      <c r="N42" s="17" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="43" spans="1:14" ht="57.6" x14ac:dyDescent="0.3">
+      <c r="A43" s="13">
+        <v>46286</v>
+      </c>
+      <c r="B43" s="14">
+        <v>420</v>
+      </c>
+      <c r="C43" s="14">
+        <v>100</v>
+      </c>
+      <c r="D43" s="14">
+        <v>135</v>
+      </c>
+      <c r="E43" s="14">
+        <v>0</v>
+      </c>
+      <c r="F43" s="14">
+        <v>0</v>
+      </c>
+      <c r="G43" s="14">
+        <v>0</v>
+      </c>
+      <c r="H43" s="14">
+        <v>495</v>
+      </c>
+      <c r="I43" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J43" s="15" t="str">
+        <v>1150</v>
+      </c>
+      <c r="J43" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K43" s="16"/>
-      <c r="L43" s="16"/>
-      <c r="M43" s="16"/>
-      <c r="N43" s="17"/>
+        <v>290</v>
+      </c>
+      <c r="K43" s="16" t="s">
+        <v>64</v>
+      </c>
+      <c r="L43" s="16" t="s">
+        <v>62</v>
+      </c>
+      <c r="M43" s="16" t="s">
+        <v>64</v>
+      </c>
+      <c r="N43" s="17" t="s">
+        <v>102</v>
+      </c>
     </row>
     <row r="44" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A44" s="13"/>

--- a/12603996.xlsx
+++ b/12603996.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://lpuin-my.sharepoint.com/personal/shubham_bither2026_lpu_in/Documents/CAP776/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="495" documentId="8_{04F8DF2E-49C5-3B44-B164-C4F738DF63B4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{81B4A34B-44D8-497D-B70E-2B67997CF4CC}"/>
+  <xr:revisionPtr revIDLastSave="507" documentId="8_{04F8DF2E-49C5-3B44-B164-C4F738DF63B4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{8ECFE9A1-8A1B-458E-9227-09053AB6F875}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13176" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="205" uniqueCount="103">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="209" uniqueCount="104">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -344,6 +344,9 @@
   </si>
   <si>
     <t>due to my medicine finished , energy level has decreased in body which is effecting my productivity</t>
+  </si>
+  <si>
+    <t xml:space="preserve">preparing for english ca </t>
   </si>
 </sst>
 </file>
@@ -2875,26 +2878,50 @@
       </c>
     </row>
     <row r="44" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A44" s="13"/>
-      <c r="B44" s="14"/>
-      <c r="C44" s="14"/>
-      <c r="D44" s="14"/>
-      <c r="E44" s="14"/>
-      <c r="F44" s="14"/>
-      <c r="G44" s="14"/>
-      <c r="H44" s="14"/>
-      <c r="I44" s="15" t="str">
+      <c r="A44" s="13">
+        <v>46287</v>
+      </c>
+      <c r="B44" s="14">
+        <v>381</v>
+      </c>
+      <c r="C44" s="14">
+        <v>80</v>
+      </c>
+      <c r="D44" s="14">
+        <v>108</v>
+      </c>
+      <c r="E44" s="14">
+        <v>0</v>
+      </c>
+      <c r="F44" s="14">
+        <v>350</v>
+      </c>
+      <c r="G44" s="14">
+        <v>7</v>
+      </c>
+      <c r="H44" s="14">
+        <v>360</v>
+      </c>
+      <c r="I44" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J44" s="15" t="str">
+        <v>1279</v>
+      </c>
+      <c r="J44" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K44" s="16"/>
-      <c r="L44" s="16"/>
-      <c r="M44" s="16"/>
-      <c r="N44" s="17"/>
+        <v>161</v>
+      </c>
+      <c r="K44" s="16" t="s">
+        <v>61</v>
+      </c>
+      <c r="L44" s="16" t="s">
+        <v>61</v>
+      </c>
+      <c r="M44" s="16" t="s">
+        <v>64</v>
+      </c>
+      <c r="N44" s="17" t="s">
+        <v>103</v>
+      </c>
     </row>
     <row r="45" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A45" s="13"/>

--- a/12603996.xlsx
+++ b/12603996.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://lpuin-my.sharepoint.com/personal/shubham_bither2026_lpu_in/Documents/CAP776/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="507" documentId="8_{04F8DF2E-49C5-3B44-B164-C4F738DF63B4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{8ECFE9A1-8A1B-458E-9227-09053AB6F875}"/>
+  <xr:revisionPtr revIDLastSave="522" documentId="8_{04F8DF2E-49C5-3B44-B164-C4F738DF63B4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{44151214-5D18-4276-86C1-43108F6792C1}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13176" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="209" uniqueCount="104">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="213" uniqueCount="105">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -347,6 +347,9 @@
   </si>
   <si>
     <t xml:space="preserve">preparing for english ca </t>
+  </si>
+  <si>
+    <t>due to prepration of english ca, I have to skip dinner</t>
   </si>
 </sst>
 </file>
@@ -2923,27 +2926,51 @@
         <v>103</v>
       </c>
     </row>
-    <row r="45" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A45" s="13"/>
-      <c r="B45" s="14"/>
-      <c r="C45" s="14"/>
-      <c r="D45" s="14"/>
-      <c r="E45" s="14"/>
-      <c r="F45" s="14"/>
-      <c r="G45" s="14"/>
-      <c r="H45" s="14"/>
-      <c r="I45" s="15" t="str">
+    <row r="45" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A45" s="13">
+        <v>46288</v>
+      </c>
+      <c r="B45" s="14">
+        <v>386</v>
+      </c>
+      <c r="C45" s="14">
+        <v>100</v>
+      </c>
+      <c r="D45" s="14">
+        <v>270</v>
+      </c>
+      <c r="E45" s="14">
+        <v>0</v>
+      </c>
+      <c r="F45" s="14">
+        <v>200</v>
+      </c>
+      <c r="G45" s="14">
+        <v>4</v>
+      </c>
+      <c r="H45" s="14">
+        <v>303</v>
+      </c>
+      <c r="I45" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J45" s="15" t="str">
+        <v>1259</v>
+      </c>
+      <c r="J45" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K45" s="16"/>
-      <c r="L45" s="16"/>
-      <c r="M45" s="16"/>
-      <c r="N45" s="17"/>
+        <v>181</v>
+      </c>
+      <c r="K45" s="16" t="s">
+        <v>61</v>
+      </c>
+      <c r="L45" s="16" t="s">
+        <v>62</v>
+      </c>
+      <c r="M45" s="16" t="s">
+        <v>51</v>
+      </c>
+      <c r="N45" s="17" t="s">
+        <v>104</v>
+      </c>
     </row>
     <row r="46" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A46" s="13"/>

--- a/12603996.xlsx
+++ b/12603996.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://lpuin-my.sharepoint.com/personal/shubham_bither2026_lpu_in/Documents/CAP776/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="522" documentId="8_{04F8DF2E-49C5-3B44-B164-C4F738DF63B4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{44151214-5D18-4276-86C1-43108F6792C1}"/>
+  <xr:revisionPtr revIDLastSave="591" documentId="8_{04F8DF2E-49C5-3B44-B164-C4F738DF63B4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{88B61149-4EB6-44D5-8870-3106D15AA091}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13176" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="213" uniqueCount="105">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="233" uniqueCount="110">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -350,6 +350,21 @@
   </si>
   <si>
     <t>due to prepration of english ca, I have to skip dinner</t>
+  </si>
+  <si>
+    <t>english ca happens today</t>
+  </si>
+  <si>
+    <t>dbms ca2 happens today, my performance was good</t>
+  </si>
+  <si>
+    <t>I submit python minor project today</t>
+  </si>
+  <si>
+    <t>today I travelled back to room from home but got news that 10 days classes are cancelled due to protest</t>
+  </si>
+  <si>
+    <t>came back home due to classes got cancelled</t>
   </si>
 </sst>
 </file>
@@ -2973,114 +2988,234 @@
       </c>
     </row>
     <row r="46" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A46" s="13"/>
-      <c r="B46" s="14"/>
-      <c r="C46" s="14"/>
-      <c r="D46" s="14"/>
-      <c r="E46" s="14"/>
-      <c r="F46" s="14"/>
-      <c r="G46" s="14"/>
-      <c r="H46" s="14"/>
-      <c r="I46" s="15" t="str">
+      <c r="A46" s="13">
+        <v>46289</v>
+      </c>
+      <c r="B46" s="14">
+        <v>331</v>
+      </c>
+      <c r="C46" s="14">
+        <v>80</v>
+      </c>
+      <c r="D46" s="14">
+        <v>135</v>
+      </c>
+      <c r="E46" s="14">
+        <v>224</v>
+      </c>
+      <c r="F46" s="14">
+        <v>350</v>
+      </c>
+      <c r="G46" s="14">
+        <v>7</v>
+      </c>
+      <c r="H46" s="14">
+        <v>234</v>
+      </c>
+      <c r="I46" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J46" s="15" t="str">
+        <v>1354</v>
+      </c>
+      <c r="J46" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K46" s="16"/>
-      <c r="L46" s="16"/>
-      <c r="M46" s="16"/>
-      <c r="N46" s="17"/>
-    </row>
-    <row r="47" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A47" s="13"/>
-      <c r="B47" s="14"/>
-      <c r="C47" s="14"/>
-      <c r="D47" s="14"/>
-      <c r="E47" s="14"/>
-      <c r="F47" s="14"/>
-      <c r="G47" s="14"/>
-      <c r="H47" s="14"/>
-      <c r="I47" s="15" t="str">
+        <v>86</v>
+      </c>
+      <c r="K46" s="16" t="s">
+        <v>61</v>
+      </c>
+      <c r="L46" s="16" t="s">
+        <v>61</v>
+      </c>
+      <c r="M46" s="16" t="s">
+        <v>64</v>
+      </c>
+      <c r="N46" s="17" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="47" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A47" s="13">
+        <v>46290</v>
+      </c>
+      <c r="B47" s="14">
+        <v>346</v>
+      </c>
+      <c r="C47" s="14">
+        <v>163</v>
+      </c>
+      <c r="D47" s="14">
+        <v>0</v>
+      </c>
+      <c r="E47" s="14">
+        <v>0</v>
+      </c>
+      <c r="F47" s="14">
+        <v>150</v>
+      </c>
+      <c r="G47" s="14">
+        <v>3</v>
+      </c>
+      <c r="H47" s="14">
+        <v>523</v>
+      </c>
+      <c r="I47" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J47" s="15" t="str">
+        <v>1182</v>
+      </c>
+      <c r="J47" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K47" s="16"/>
-      <c r="L47" s="16"/>
-      <c r="M47" s="16"/>
-      <c r="N47" s="17"/>
-    </row>
-    <row r="48" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A48" s="13"/>
-      <c r="B48" s="14"/>
-      <c r="C48" s="14"/>
-      <c r="D48" s="14"/>
-      <c r="E48" s="14"/>
-      <c r="F48" s="14"/>
-      <c r="G48" s="14"/>
-      <c r="H48" s="14"/>
-      <c r="I48" s="15" t="str">
+        <v>258</v>
+      </c>
+      <c r="K47" s="16" t="s">
+        <v>49</v>
+      </c>
+      <c r="L47" s="16" t="s">
+        <v>61</v>
+      </c>
+      <c r="M47" s="16" t="s">
+        <v>51</v>
+      </c>
+      <c r="N47" s="17" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="48" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A48" s="13">
+        <v>46291</v>
+      </c>
+      <c r="B48" s="14">
+        <v>587</v>
+      </c>
+      <c r="C48" s="14">
+        <v>0</v>
+      </c>
+      <c r="D48" s="14">
+        <v>181</v>
+      </c>
+      <c r="E48" s="14">
+        <v>245</v>
+      </c>
+      <c r="F48" s="14">
+        <v>0</v>
+      </c>
+      <c r="G48" s="14">
+        <v>0</v>
+      </c>
+      <c r="H48" s="14">
+        <v>427</v>
+      </c>
+      <c r="I48" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J48" s="15" t="str">
+        <v>1440</v>
+      </c>
+      <c r="J48" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K48" s="16"/>
-      <c r="L48" s="16"/>
-      <c r="M48" s="16"/>
-      <c r="N48" s="17"/>
-    </row>
-    <row r="49" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A49" s="13"/>
-      <c r="B49" s="14"/>
-      <c r="C49" s="14"/>
-      <c r="D49" s="14"/>
-      <c r="E49" s="14"/>
-      <c r="F49" s="14"/>
-      <c r="G49" s="14"/>
-      <c r="H49" s="14"/>
-      <c r="I49" s="15" t="str">
+        <v>0</v>
+      </c>
+      <c r="K48" s="16" t="s">
+        <v>49</v>
+      </c>
+      <c r="L48" s="16" t="s">
+        <v>50</v>
+      </c>
+      <c r="M48" s="16" t="s">
+        <v>64</v>
+      </c>
+      <c r="N48" s="17" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="49" spans="1:14" ht="57.6" x14ac:dyDescent="0.3">
+      <c r="A49" s="13">
+        <v>46292</v>
+      </c>
+      <c r="B49" s="14">
+        <v>366</v>
+      </c>
+      <c r="C49" s="14">
+        <v>80</v>
+      </c>
+      <c r="D49" s="14">
+        <v>0</v>
+      </c>
+      <c r="E49" s="14">
+        <v>0</v>
+      </c>
+      <c r="F49" s="14">
+        <v>0</v>
+      </c>
+      <c r="G49" s="14">
+        <v>0</v>
+      </c>
+      <c r="H49" s="14">
+        <v>824</v>
+      </c>
+      <c r="I49" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J49" s="15" t="str">
+        <v>1270</v>
+      </c>
+      <c r="J49" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K49" s="16"/>
-      <c r="L49" s="16"/>
-      <c r="M49" s="16"/>
-      <c r="N49" s="17"/>
-    </row>
-    <row r="50" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A50" s="13"/>
-      <c r="B50" s="14"/>
-      <c r="C50" s="14"/>
-      <c r="D50" s="14"/>
-      <c r="E50" s="14"/>
-      <c r="F50" s="14"/>
-      <c r="G50" s="14"/>
-      <c r="H50" s="14"/>
-      <c r="I50" s="15" t="str">
+        <v>170</v>
+      </c>
+      <c r="K49" s="16" t="s">
+        <v>67</v>
+      </c>
+      <c r="L49" s="16" t="s">
+        <v>68</v>
+      </c>
+      <c r="M49" s="16" t="s">
+        <v>64</v>
+      </c>
+      <c r="N49" s="17" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="50" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A50" s="13">
+        <v>46293</v>
+      </c>
+      <c r="B50" s="14">
+        <v>337</v>
+      </c>
+      <c r="C50" s="14">
+        <v>80</v>
+      </c>
+      <c r="D50" s="14">
+        <v>0</v>
+      </c>
+      <c r="E50" s="14">
+        <v>0</v>
+      </c>
+      <c r="F50" s="14">
+        <v>0</v>
+      </c>
+      <c r="G50" s="14">
+        <v>0</v>
+      </c>
+      <c r="H50" s="14">
+        <v>882</v>
+      </c>
+      <c r="I50" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J50" s="15" t="str">
+        <v>1299</v>
+      </c>
+      <c r="J50" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K50" s="16"/>
-      <c r="L50" s="16"/>
-      <c r="M50" s="16"/>
-      <c r="N50" s="17"/>
+        <v>141</v>
+      </c>
+      <c r="K50" s="16" t="s">
+        <v>64</v>
+      </c>
+      <c r="L50" s="16" t="s">
+        <v>62</v>
+      </c>
+      <c r="M50" s="16" t="s">
+        <v>64</v>
+      </c>
+      <c r="N50" s="17" t="s">
+        <v>109</v>
+      </c>
     </row>
     <row r="51" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A51" s="13"/>

--- a/12603996.xlsx
+++ b/12603996.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30430"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://lpuin-my.sharepoint.com/personal/shubham_bither2026_lpu_in/Documents/CAP776/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="591" documentId="8_{04F8DF2E-49C5-3B44-B164-C4F738DF63B4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{88B61149-4EB6-44D5-8870-3106D15AA091}"/>
+  <xr:revisionPtr revIDLastSave="615" documentId="8_{04F8DF2E-49C5-3B44-B164-C4F738DF63B4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{671FAE3C-EB00-4750-867B-21353B7D6C8F}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13176" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="233" uniqueCount="110">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="241" uniqueCount="112">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -365,6 +365,12 @@
   </si>
   <si>
     <t>came back home due to classes got cancelled</t>
+  </si>
+  <si>
+    <t>not able to study enogh due to headache</t>
+  </si>
+  <si>
+    <t>test drive new bike for brother</t>
   </si>
 </sst>
 </file>
@@ -3217,49 +3223,97 @@
         <v>109</v>
       </c>
     </row>
-    <row r="51" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A51" s="13"/>
-      <c r="B51" s="14"/>
-      <c r="C51" s="14"/>
-      <c r="D51" s="14"/>
-      <c r="E51" s="14"/>
-      <c r="F51" s="14"/>
-      <c r="G51" s="14"/>
-      <c r="H51" s="14"/>
-      <c r="I51" s="15" t="str">
+    <row r="51" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A51" s="13">
+        <v>46294</v>
+      </c>
+      <c r="B51" s="14">
+        <v>583</v>
+      </c>
+      <c r="C51" s="14">
+        <v>0</v>
+      </c>
+      <c r="D51" s="14">
+        <v>152</v>
+      </c>
+      <c r="E51" s="14">
+        <v>0</v>
+      </c>
+      <c r="F51" s="14">
+        <v>0</v>
+      </c>
+      <c r="G51" s="14">
+        <v>0</v>
+      </c>
+      <c r="H51" s="14">
+        <v>654</v>
+      </c>
+      <c r="I51" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J51" s="15" t="str">
+        <v>1389</v>
+      </c>
+      <c r="J51" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K51" s="16"/>
-      <c r="L51" s="16"/>
-      <c r="M51" s="16"/>
-      <c r="N51" s="17"/>
+        <v>51</v>
+      </c>
+      <c r="K51" s="16" t="s">
+        <v>64</v>
+      </c>
+      <c r="L51" s="16" t="s">
+        <v>62</v>
+      </c>
+      <c r="M51" s="16" t="s">
+        <v>51</v>
+      </c>
+      <c r="N51" s="17" t="s">
+        <v>110</v>
+      </c>
     </row>
     <row r="52" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A52" s="13"/>
-      <c r="B52" s="14"/>
-      <c r="C52" s="14"/>
-      <c r="D52" s="14"/>
-      <c r="E52" s="14"/>
-      <c r="F52" s="14"/>
-      <c r="G52" s="14"/>
-      <c r="H52" s="14"/>
-      <c r="I52" s="15" t="str">
+      <c r="A52" s="13">
+        <v>46295</v>
+      </c>
+      <c r="B52" s="14">
+        <v>451</v>
+      </c>
+      <c r="C52" s="14">
+        <v>17</v>
+      </c>
+      <c r="D52" s="14">
+        <v>120</v>
+      </c>
+      <c r="E52" s="14">
+        <v>0</v>
+      </c>
+      <c r="F52" s="14">
+        <v>0</v>
+      </c>
+      <c r="G52" s="14">
+        <v>0</v>
+      </c>
+      <c r="H52" s="14">
+        <v>655</v>
+      </c>
+      <c r="I52" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J52" s="15" t="str">
+        <v>1243</v>
+      </c>
+      <c r="J52" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K52" s="16"/>
-      <c r="L52" s="16"/>
-      <c r="M52" s="16"/>
-      <c r="N52" s="17"/>
+        <v>197</v>
+      </c>
+      <c r="K52" s="16" t="s">
+        <v>64</v>
+      </c>
+      <c r="L52" s="16" t="s">
+        <v>62</v>
+      </c>
+      <c r="M52" s="16" t="s">
+        <v>51</v>
+      </c>
+      <c r="N52" s="17" t="s">
+        <v>111</v>
+      </c>
     </row>
     <row r="53" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A53" s="13"/>

--- a/12603996.xlsx
+++ b/12603996.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://lpuin-my.sharepoint.com/personal/shubham_bither2026_lpu_in/Documents/CAP776/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="615" documentId="8_{04F8DF2E-49C5-3B44-B164-C4F738DF63B4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{671FAE3C-EB00-4750-867B-21353B7D6C8F}"/>
+  <xr:revisionPtr revIDLastSave="639" documentId="8_{04F8DF2E-49C5-3B44-B164-C4F738DF63B4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{3CF2D0E6-2DCF-4A3E-9DF7-98D76BD29038}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13176" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="241" uniqueCount="112">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="249" uniqueCount="114">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -371,6 +371,12 @@
   </si>
   <si>
     <t>test drive new bike for brother</t>
+  </si>
+  <si>
+    <t>started preparing for mid-term</t>
+  </si>
+  <si>
+    <t>arrived at nani house</t>
   </si>
 </sst>
 </file>
@@ -3316,48 +3322,96 @@
       </c>
     </row>
     <row r="53" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A53" s="13"/>
-      <c r="B53" s="14"/>
-      <c r="C53" s="14"/>
-      <c r="D53" s="14"/>
-      <c r="E53" s="14"/>
-      <c r="F53" s="14"/>
-      <c r="G53" s="14"/>
-      <c r="H53" s="14"/>
-      <c r="I53" s="15" t="str">
+      <c r="A53" s="13">
+        <v>46296</v>
+      </c>
+      <c r="B53" s="14">
+        <v>493</v>
+      </c>
+      <c r="C53" s="14">
+        <v>0</v>
+      </c>
+      <c r="D53" s="14">
+        <v>125</v>
+      </c>
+      <c r="E53" s="14">
+        <v>0</v>
+      </c>
+      <c r="F53" s="14">
+        <v>0</v>
+      </c>
+      <c r="G53" s="14">
+        <v>0</v>
+      </c>
+      <c r="H53" s="14">
+        <v>655</v>
+      </c>
+      <c r="I53" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J53" s="15" t="str">
+        <v>1273</v>
+      </c>
+      <c r="J53" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K53" s="16"/>
-      <c r="L53" s="16"/>
-      <c r="M53" s="16"/>
-      <c r="N53" s="17"/>
+        <v>167</v>
+      </c>
+      <c r="K53" s="16" t="s">
+        <v>64</v>
+      </c>
+      <c r="L53" s="16" t="s">
+        <v>62</v>
+      </c>
+      <c r="M53" s="16" t="s">
+        <v>64</v>
+      </c>
+      <c r="N53" s="17" t="s">
+        <v>112</v>
+      </c>
     </row>
     <row r="54" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A54" s="13"/>
-      <c r="B54" s="14"/>
-      <c r="C54" s="14"/>
-      <c r="D54" s="14"/>
-      <c r="E54" s="14"/>
-      <c r="F54" s="14"/>
-      <c r="G54" s="14"/>
-      <c r="H54" s="14"/>
-      <c r="I54" s="15" t="str">
+      <c r="A54" s="13">
+        <v>46297</v>
+      </c>
+      <c r="B54" s="14">
+        <v>324</v>
+      </c>
+      <c r="C54" s="14">
+        <v>40</v>
+      </c>
+      <c r="D54" s="14">
+        <v>90</v>
+      </c>
+      <c r="E54" s="14">
+        <v>0</v>
+      </c>
+      <c r="F54" s="14">
+        <v>0</v>
+      </c>
+      <c r="G54" s="14">
+        <v>0</v>
+      </c>
+      <c r="H54" s="14">
+        <v>886</v>
+      </c>
+      <c r="I54" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J54" s="15" t="str">
+        <v>1340</v>
+      </c>
+      <c r="J54" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K54" s="16"/>
-      <c r="L54" s="16"/>
-      <c r="M54" s="16"/>
-      <c r="N54" s="17"/>
+        <v>100</v>
+      </c>
+      <c r="K54" s="16" t="s">
+        <v>49</v>
+      </c>
+      <c r="L54" s="16" t="s">
+        <v>61</v>
+      </c>
+      <c r="M54" s="16" t="s">
+        <v>64</v>
+      </c>
+      <c r="N54" s="17" t="s">
+        <v>113</v>
+      </c>
     </row>
     <row r="55" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A55" s="13"/>

--- a/12603996.xlsx
+++ b/12603996.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://lpuin-my.sharepoint.com/personal/shubham_bither2026_lpu_in/Documents/CAP776/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="639" documentId="8_{04F8DF2E-49C5-3B44-B164-C4F738DF63B4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{3CF2D0E6-2DCF-4A3E-9DF7-98D76BD29038}"/>
+  <xr:revisionPtr revIDLastSave="653" documentId="8_{04F8DF2E-49C5-3B44-B164-C4F738DF63B4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{625D2DB1-E845-4D26-9EC9-E907FABAF3BC}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13176" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="249" uniqueCount="114">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="253" uniqueCount="115">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -377,6 +377,9 @@
   </si>
   <si>
     <t>arrived at nani house</t>
+  </si>
+  <si>
+    <t>planned to go for shopping,but it didn't happen</t>
   </si>
 </sst>
 </file>
@@ -3413,27 +3416,51 @@
         <v>113</v>
       </c>
     </row>
-    <row r="55" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A55" s="13"/>
-      <c r="B55" s="14"/>
-      <c r="C55" s="14"/>
-      <c r="D55" s="14"/>
-      <c r="E55" s="14"/>
-      <c r="F55" s="14"/>
-      <c r="G55" s="14"/>
-      <c r="H55" s="14"/>
-      <c r="I55" s="15" t="str">
+    <row r="55" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A55" s="13">
+        <v>46298</v>
+      </c>
+      <c r="B55" s="14">
+        <v>421</v>
+      </c>
+      <c r="C55" s="14">
+        <v>45</v>
+      </c>
+      <c r="D55" s="14">
+        <v>240</v>
+      </c>
+      <c r="E55" s="14">
+        <v>0</v>
+      </c>
+      <c r="F55" s="14">
+        <v>0</v>
+      </c>
+      <c r="G55" s="14">
+        <v>0</v>
+      </c>
+      <c r="H55" s="14">
+        <v>655</v>
+      </c>
+      <c r="I55" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J55" s="15" t="str">
+        <v>1361</v>
+      </c>
+      <c r="J55" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K55" s="16"/>
-      <c r="L55" s="16"/>
-      <c r="M55" s="16"/>
-      <c r="N55" s="17"/>
+        <v>79</v>
+      </c>
+      <c r="K55" s="16" t="s">
+        <v>61</v>
+      </c>
+      <c r="L55" s="16" t="s">
+        <v>61</v>
+      </c>
+      <c r="M55" s="16" t="s">
+        <v>51</v>
+      </c>
+      <c r="N55" s="17" t="s">
+        <v>114</v>
+      </c>
     </row>
     <row r="56" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A56" s="13"/>

--- a/12603996.xlsx
+++ b/12603996.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://lpuin-my.sharepoint.com/personal/shubham_bither2026_lpu_in/Documents/CAP776/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="694" documentId="8_{04F8DF2E-49C5-3B44-B164-C4F738DF63B4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{FB0A0890-F462-4B68-92A9-6BC5A9EA72D3}"/>
+  <xr:revisionPtr revIDLastSave="720" documentId="8_{04F8DF2E-49C5-3B44-B164-C4F738DF63B4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{DAD3ED8A-4BED-4160-B2A0-B57CF97CA912}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13176" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="261" uniqueCount="116">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="269" uniqueCount="118">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -383,6 +383,12 @@
   </si>
   <si>
     <t>nothing happened today.just a basic day</t>
+  </si>
+  <si>
+    <t>networking ca preparation finished</t>
+  </si>
+  <si>
+    <t>order new table</t>
   </si>
 </sst>
 </file>
@@ -3535,49 +3541,97 @@
         <v>115</v>
       </c>
     </row>
-    <row r="58" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A58" s="8"/>
-      <c r="B58" s="9"/>
-      <c r="C58" s="9"/>
-      <c r="D58" s="9"/>
-      <c r="E58" s="9"/>
-      <c r="F58" s="9"/>
-      <c r="G58" s="9"/>
-      <c r="H58" s="9"/>
-      <c r="I58" s="10" t="str">
+    <row r="58" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A58" s="8">
+        <v>46302</v>
+      </c>
+      <c r="B58" s="9">
+        <v>510</v>
+      </c>
+      <c r="C58" s="9">
+        <v>0</v>
+      </c>
+      <c r="D58" s="9">
+        <v>236</v>
+      </c>
+      <c r="E58" s="9">
+        <v>0</v>
+      </c>
+      <c r="F58" s="9">
+        <v>150</v>
+      </c>
+      <c r="G58" s="9">
+        <v>3</v>
+      </c>
+      <c r="H58" s="9">
+        <v>523</v>
+      </c>
+      <c r="I58" s="10">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J58" s="10" t="str">
+        <v>1419</v>
+      </c>
+      <c r="J58" s="10">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K58" s="11"/>
-      <c r="L58" s="11"/>
-      <c r="M58" s="11"/>
-      <c r="N58" s="12"/>
+        <v>21</v>
+      </c>
+      <c r="K58" s="11" t="s">
+        <v>66</v>
+      </c>
+      <c r="L58" s="11" t="s">
+        <v>61</v>
+      </c>
+      <c r="M58" s="11" t="s">
+        <v>51</v>
+      </c>
+      <c r="N58" s="12" t="s">
+        <v>116</v>
+      </c>
     </row>
     <row r="59" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A59" s="8"/>
-      <c r="B59" s="9"/>
-      <c r="C59" s="9"/>
-      <c r="D59" s="9"/>
-      <c r="E59" s="9"/>
-      <c r="F59" s="9"/>
-      <c r="G59" s="9"/>
-      <c r="H59" s="9"/>
-      <c r="I59" s="10" t="str">
+      <c r="A59" s="8">
+        <v>46303</v>
+      </c>
+      <c r="B59" s="9">
+        <v>463</v>
+      </c>
+      <c r="C59" s="9">
+        <v>0</v>
+      </c>
+      <c r="D59" s="9">
+        <v>346</v>
+      </c>
+      <c r="E59" s="9">
+        <v>0</v>
+      </c>
+      <c r="F59" s="9">
+        <v>0</v>
+      </c>
+      <c r="G59" s="9">
+        <v>0</v>
+      </c>
+      <c r="H59" s="9">
+        <v>450</v>
+      </c>
+      <c r="I59" s="10">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J59" s="10" t="str">
+        <v>1259</v>
+      </c>
+      <c r="J59" s="10">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K59" s="11"/>
-      <c r="L59" s="11"/>
-      <c r="M59" s="11"/>
-      <c r="N59" s="12"/>
+        <v>181</v>
+      </c>
+      <c r="K59" s="11" t="s">
+        <v>63</v>
+      </c>
+      <c r="L59" s="11" t="s">
+        <v>61</v>
+      </c>
+      <c r="M59" s="11" t="s">
+        <v>51</v>
+      </c>
+      <c r="N59" s="12" t="s">
+        <v>117</v>
+      </c>
     </row>
     <row r="60" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A60" s="8"/>

--- a/12603996.xlsx
+++ b/12603996.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://lpuin-my.sharepoint.com/personal/shubham_bither2026_lpu_in/Documents/CAP776/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="720" documentId="8_{04F8DF2E-49C5-3B44-B164-C4F738DF63B4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{DAD3ED8A-4BED-4160-B2A0-B57CF97CA912}"/>
+  <xr:revisionPtr revIDLastSave="823" documentId="8_{04F8DF2E-49C5-3B44-B164-C4F738DF63B4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{C58E405B-7D29-47C6-9EB6-3BE3AD937001}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13176" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="269" uniqueCount="118">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="301" uniqueCount="126">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -389,6 +389,30 @@
   </si>
   <si>
     <t>order new table</t>
+  </si>
+  <si>
+    <t>5 hrs 30 min spent on bike service</t>
+  </si>
+  <si>
+    <t>whole day was consumed in packing and travelling</t>
+  </si>
+  <si>
+    <t>networking paper went good and prepared for c++ paper</t>
+  </si>
+  <si>
+    <t xml:space="preserve">maths and netoworking paper preparation </t>
+  </si>
+  <si>
+    <t>prepared for db paper</t>
+  </si>
+  <si>
+    <t>new table arrived and it consumed time , db paper was very easy</t>
+  </si>
+  <si>
+    <t>today whole day I studied for maths paper</t>
+  </si>
+  <si>
+    <t>maths paper was good and studied for english paper, started dexter</t>
   </si>
 </sst>
 </file>
@@ -3633,181 +3657,373 @@
         <v>117</v>
       </c>
     </row>
-    <row r="60" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A60" s="8"/>
-      <c r="B60" s="9"/>
-      <c r="C60" s="9"/>
-      <c r="D60" s="9"/>
-      <c r="E60" s="9"/>
-      <c r="F60" s="9"/>
-      <c r="G60" s="9"/>
-      <c r="H60" s="9"/>
-      <c r="I60" s="10" t="str">
+    <row r="60" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A60" s="8">
+        <v>46304</v>
+      </c>
+      <c r="B60" s="9">
+        <v>333</v>
+      </c>
+      <c r="C60" s="9">
+        <v>126</v>
+      </c>
+      <c r="D60" s="9">
+        <v>125</v>
+      </c>
+      <c r="E60" s="9">
+        <v>0</v>
+      </c>
+      <c r="F60" s="9">
+        <v>0</v>
+      </c>
+      <c r="G60" s="9">
+        <v>0</v>
+      </c>
+      <c r="H60" s="9">
+        <v>570</v>
+      </c>
+      <c r="I60" s="10">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J60" s="10" t="str">
+        <v>1154</v>
+      </c>
+      <c r="J60" s="10">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K60" s="11"/>
-      <c r="L60" s="11"/>
-      <c r="M60" s="11"/>
-      <c r="N60" s="12"/>
-    </row>
-    <row r="61" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A61" s="8"/>
-      <c r="B61" s="9"/>
-      <c r="C61" s="9"/>
-      <c r="D61" s="9"/>
-      <c r="E61" s="9"/>
-      <c r="F61" s="9"/>
-      <c r="G61" s="9"/>
-      <c r="H61" s="9"/>
-      <c r="I61" s="10" t="str">
+        <v>286</v>
+      </c>
+      <c r="K60" s="11" t="s">
+        <v>60</v>
+      </c>
+      <c r="L60" s="11" t="s">
+        <v>61</v>
+      </c>
+      <c r="M60" s="11" t="s">
+        <v>63</v>
+      </c>
+      <c r="N60" s="12" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="61" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A61" s="8">
+        <v>46305</v>
+      </c>
+      <c r="B61" s="9">
+        <v>438</v>
+      </c>
+      <c r="C61" s="9">
+        <v>42</v>
+      </c>
+      <c r="D61" s="9">
+        <v>0</v>
+      </c>
+      <c r="E61" s="9">
+        <v>0</v>
+      </c>
+      <c r="F61" s="9">
+        <v>0</v>
+      </c>
+      <c r="G61" s="9">
+        <v>0</v>
+      </c>
+      <c r="H61" s="9">
+        <v>882</v>
+      </c>
+      <c r="I61" s="10">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J61" s="10" t="str">
+        <v>1362</v>
+      </c>
+      <c r="J61" s="10">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K61" s="11"/>
-      <c r="L61" s="11"/>
-      <c r="M61" s="11"/>
-      <c r="N61" s="12"/>
-    </row>
-    <row r="62" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A62" s="8"/>
-      <c r="B62" s="9"/>
-      <c r="C62" s="9"/>
-      <c r="D62" s="9"/>
-      <c r="E62" s="9"/>
-      <c r="F62" s="9"/>
-      <c r="G62" s="9"/>
-      <c r="H62" s="9"/>
-      <c r="I62" s="10" t="str">
+        <v>78</v>
+      </c>
+      <c r="K61" s="11" t="s">
+        <v>63</v>
+      </c>
+      <c r="L61" s="11" t="s">
+        <v>61</v>
+      </c>
+      <c r="M61" s="11" t="s">
+        <v>63</v>
+      </c>
+      <c r="N61" s="12" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="62" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A62" s="8">
+        <v>46306</v>
+      </c>
+      <c r="B62" s="9">
+        <v>425</v>
+      </c>
+      <c r="C62" s="9">
+        <v>56</v>
+      </c>
+      <c r="D62" s="9">
+        <v>522</v>
+      </c>
+      <c r="E62" s="9">
+        <v>0</v>
+      </c>
+      <c r="F62" s="9">
+        <v>0</v>
+      </c>
+      <c r="G62" s="9">
+        <v>0</v>
+      </c>
+      <c r="H62" s="9">
+        <v>425</v>
+      </c>
+      <c r="I62" s="10">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J62" s="10" t="str">
+        <v>1428</v>
+      </c>
+      <c r="J62" s="10">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K62" s="11"/>
-      <c r="L62" s="11"/>
-      <c r="M62" s="11"/>
-      <c r="N62" s="12"/>
-    </row>
-    <row r="63" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A63" s="8"/>
-      <c r="B63" s="9"/>
-      <c r="C63" s="9"/>
-      <c r="D63" s="9"/>
-      <c r="E63" s="9"/>
-      <c r="F63" s="9"/>
-      <c r="G63" s="9"/>
-      <c r="H63" s="9"/>
-      <c r="I63" s="10" t="str">
+        <v>12</v>
+      </c>
+      <c r="K62" s="11" t="s">
+        <v>60</v>
+      </c>
+      <c r="L62" s="11" t="s">
+        <v>60</v>
+      </c>
+      <c r="M62" s="11" t="s">
+        <v>51</v>
+      </c>
+      <c r="N62" s="12" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="63" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A63" s="8">
+        <v>46307</v>
+      </c>
+      <c r="B63" s="9">
+        <v>372</v>
+      </c>
+      <c r="C63" s="9">
+        <v>102</v>
+      </c>
+      <c r="D63" s="9">
+        <v>457</v>
+      </c>
+      <c r="E63" s="9">
+        <v>0</v>
+      </c>
+      <c r="F63" s="9">
+        <v>0</v>
+      </c>
+      <c r="G63" s="9">
+        <v>0</v>
+      </c>
+      <c r="H63" s="9">
+        <v>435</v>
+      </c>
+      <c r="I63" s="10">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J63" s="10" t="str">
+        <v>1366</v>
+      </c>
+      <c r="J63" s="10">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K63" s="11"/>
-      <c r="L63" s="11"/>
-      <c r="M63" s="11"/>
-      <c r="N63" s="12"/>
+        <v>74</v>
+      </c>
+      <c r="K63" s="11" t="s">
+        <v>49</v>
+      </c>
+      <c r="L63" s="11" t="s">
+        <v>50</v>
+      </c>
+      <c r="M63" s="11" t="s">
+        <v>51</v>
+      </c>
+      <c r="N63" s="12" t="s">
+        <v>120</v>
+      </c>
     </row>
     <row r="64" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A64" s="8"/>
-      <c r="B64" s="9"/>
-      <c r="C64" s="9"/>
-      <c r="D64" s="9"/>
-      <c r="E64" s="9"/>
-      <c r="F64" s="9"/>
-      <c r="G64" s="9"/>
-      <c r="H64" s="9"/>
-      <c r="I64" s="10" t="str">
+      <c r="A64" s="8">
+        <v>46308</v>
+      </c>
+      <c r="B64" s="9">
+        <v>312</v>
+      </c>
+      <c r="C64" s="9">
+        <v>82</v>
+      </c>
+      <c r="D64" s="9">
+        <v>463</v>
+      </c>
+      <c r="E64" s="9">
+        <v>0</v>
+      </c>
+      <c r="F64" s="9">
+        <v>0</v>
+      </c>
+      <c r="G64" s="9">
+        <v>0</v>
+      </c>
+      <c r="H64" s="9">
+        <v>455</v>
+      </c>
+      <c r="I64" s="10">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J64" s="10" t="str">
+        <v>1312</v>
+      </c>
+      <c r="J64" s="10">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K64" s="11"/>
-      <c r="L64" s="11"/>
-      <c r="M64" s="11"/>
-      <c r="N64" s="12"/>
-    </row>
-    <row r="65" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A65" s="8"/>
-      <c r="B65" s="9"/>
-      <c r="C65" s="9"/>
-      <c r="D65" s="9"/>
-      <c r="E65" s="9"/>
-      <c r="F65" s="9"/>
-      <c r="G65" s="9"/>
-      <c r="H65" s="9"/>
-      <c r="I65" s="10" t="str">
+        <v>128</v>
+      </c>
+      <c r="K64" s="11" t="s">
+        <v>60</v>
+      </c>
+      <c r="L64" s="11" t="s">
+        <v>60</v>
+      </c>
+      <c r="M64" s="11" t="s">
+        <v>63</v>
+      </c>
+      <c r="N64" s="12" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="65" spans="1:14" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A65" s="8">
+        <v>46309</v>
+      </c>
+      <c r="B65" s="9">
+        <v>312</v>
+      </c>
+      <c r="C65" s="9">
+        <v>60</v>
+      </c>
+      <c r="D65" s="9">
+        <v>369</v>
+      </c>
+      <c r="E65" s="9">
+        <v>0</v>
+      </c>
+      <c r="F65" s="9">
+        <v>0</v>
+      </c>
+      <c r="G65" s="9">
+        <v>0</v>
+      </c>
+      <c r="H65" s="9">
+        <v>423</v>
+      </c>
+      <c r="I65" s="10">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J65" s="10" t="str">
+        <v>1164</v>
+      </c>
+      <c r="J65" s="10">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K65" s="11"/>
-      <c r="L65" s="11"/>
-      <c r="M65" s="11"/>
-      <c r="N65" s="12"/>
-    </row>
-    <row r="66" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A66" s="8"/>
-      <c r="B66" s="9"/>
-      <c r="C66" s="9"/>
-      <c r="D66" s="9"/>
-      <c r="E66" s="9"/>
-      <c r="F66" s="9"/>
-      <c r="G66" s="9"/>
-      <c r="H66" s="9"/>
-      <c r="I66" s="10" t="str">
+        <v>276</v>
+      </c>
+      <c r="K65" s="11" t="s">
+        <v>60</v>
+      </c>
+      <c r="L65" s="11" t="s">
+        <v>60</v>
+      </c>
+      <c r="M65" s="11" t="s">
+        <v>63</v>
+      </c>
+      <c r="N65" s="12" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="66" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A66" s="8">
+        <v>46310</v>
+      </c>
+      <c r="B66" s="9">
+        <v>315</v>
+      </c>
+      <c r="C66" s="9">
+        <v>114</v>
+      </c>
+      <c r="D66" s="9">
+        <v>623</v>
+      </c>
+      <c r="E66" s="9">
+        <v>0</v>
+      </c>
+      <c r="F66" s="9">
+        <v>0</v>
+      </c>
+      <c r="G66" s="9">
+        <v>0</v>
+      </c>
+      <c r="H66" s="9">
+        <v>326</v>
+      </c>
+      <c r="I66" s="10">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J66" s="10" t="str">
+        <v>1378</v>
+      </c>
+      <c r="J66" s="10">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K66" s="11"/>
-      <c r="L66" s="11"/>
-      <c r="M66" s="11"/>
-      <c r="N66" s="12"/>
-    </row>
-    <row r="67" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A67" s="8"/>
-      <c r="B67" s="9"/>
-      <c r="C67" s="9"/>
-      <c r="D67" s="9"/>
-      <c r="E67" s="9"/>
-      <c r="F67" s="9"/>
-      <c r="G67" s="9"/>
-      <c r="H67" s="9"/>
-      <c r="I67" s="10" t="str">
+        <v>62</v>
+      </c>
+      <c r="K66" s="11" t="s">
+        <v>49</v>
+      </c>
+      <c r="L66" s="11" t="s">
+        <v>60</v>
+      </c>
+      <c r="M66" s="11" t="s">
+        <v>51</v>
+      </c>
+      <c r="N66" s="12" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="67" spans="1:14" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A67" s="8">
+        <v>46311</v>
+      </c>
+      <c r="B67" s="9">
+        <v>347</v>
+      </c>
+      <c r="C67" s="9">
+        <v>62</v>
+      </c>
+      <c r="D67" s="9">
+        <v>420</v>
+      </c>
+      <c r="E67" s="9">
+        <v>0</v>
+      </c>
+      <c r="F67" s="9">
+        <v>0</v>
+      </c>
+      <c r="G67" s="9">
+        <v>0</v>
+      </c>
+      <c r="H67" s="9">
+        <v>555</v>
+      </c>
+      <c r="I67" s="10">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J67" s="10" t="str">
+        <v>1384</v>
+      </c>
+      <c r="J67" s="10">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K67" s="11"/>
-      <c r="L67" s="11"/>
-      <c r="M67" s="11"/>
-      <c r="N67" s="12"/>
+        <v>56</v>
+      </c>
+      <c r="K67" s="11" t="s">
+        <v>49</v>
+      </c>
+      <c r="L67" s="11" t="s">
+        <v>60</v>
+      </c>
+      <c r="M67" s="11" t="s">
+        <v>63</v>
+      </c>
+      <c r="N67" s="12" t="s">
+        <v>125</v>
+      </c>
     </row>
     <row r="68" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A68" s="8"/>

--- a/12603996.xlsx
+++ b/12603996.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://lpuin-my.sharepoint.com/personal/shubham_bither2026_lpu_in/Documents/CAP776/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="823" documentId="8_{04F8DF2E-49C5-3B44-B164-C4F738DF63B4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{C58E405B-7D29-47C6-9EB6-3BE3AD937001}"/>
+  <xr:revisionPtr revIDLastSave="875" documentId="8_{04F8DF2E-49C5-3B44-B164-C4F738DF63B4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{3233D9BD-7FFF-4F38-A1A5-C511A2A29D9D}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13176" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="301" uniqueCount="126">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="317" uniqueCount="130">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -413,6 +413,18 @@
   </si>
   <si>
     <t>maths paper was good and studied for english paper, started dexter</t>
+  </si>
+  <si>
+    <t>went to home after paper</t>
+  </si>
+  <si>
+    <t>watched dexter whole day</t>
+  </si>
+  <si>
+    <t>finished dexter s1 and revise dsa</t>
+  </si>
+  <si>
+    <t>happy dusshera</t>
   </si>
 </sst>
 </file>
@@ -4026,92 +4038,188 @@
       </c>
     </row>
     <row r="68" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A68" s="8"/>
-      <c r="B68" s="9"/>
-      <c r="C68" s="9"/>
-      <c r="D68" s="9"/>
-      <c r="E68" s="9"/>
-      <c r="F68" s="9"/>
-      <c r="G68" s="9"/>
-      <c r="H68" s="9"/>
-      <c r="I68" s="10" t="str">
+      <c r="A68" s="8">
+        <v>46312</v>
+      </c>
+      <c r="B68" s="9">
+        <v>347</v>
+      </c>
+      <c r="C68" s="9">
+        <v>102</v>
+      </c>
+      <c r="D68" s="9">
+        <v>156</v>
+      </c>
+      <c r="E68" s="9">
+        <v>0</v>
+      </c>
+      <c r="F68" s="9">
+        <v>0</v>
+      </c>
+      <c r="G68" s="9">
+        <v>0</v>
+      </c>
+      <c r="H68" s="9">
+        <v>835</v>
+      </c>
+      <c r="I68" s="10">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J68" s="10" t="str">
+        <v>1440</v>
+      </c>
+      <c r="J68" s="10">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K68" s="11"/>
-      <c r="L68" s="11"/>
-      <c r="M68" s="11"/>
-      <c r="N68" s="12"/>
+        <v>0</v>
+      </c>
+      <c r="K68" s="11" t="s">
+        <v>60</v>
+      </c>
+      <c r="L68" s="11" t="s">
+        <v>60</v>
+      </c>
+      <c r="M68" s="11" t="s">
+        <v>51</v>
+      </c>
+      <c r="N68" s="12" t="s">
+        <v>126</v>
+      </c>
     </row>
     <row r="69" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A69" s="8"/>
-      <c r="B69" s="9"/>
-      <c r="C69" s="9"/>
-      <c r="D69" s="9"/>
-      <c r="E69" s="9"/>
-      <c r="F69" s="9"/>
-      <c r="G69" s="9"/>
-      <c r="H69" s="9"/>
-      <c r="I69" s="10" t="str">
+      <c r="A69" s="8">
+        <v>46313</v>
+      </c>
+      <c r="B69" s="9">
+        <v>612</v>
+      </c>
+      <c r="C69" s="9">
+        <v>0</v>
+      </c>
+      <c r="D69" s="9">
+        <v>0</v>
+      </c>
+      <c r="E69" s="9">
+        <v>0</v>
+      </c>
+      <c r="F69" s="9">
+        <v>0</v>
+      </c>
+      <c r="G69" s="9">
+        <v>0</v>
+      </c>
+      <c r="H69" s="9">
+        <v>789</v>
+      </c>
+      <c r="I69" s="10">
         <f t="shared" ref="I69:I132" si="2">IF(SUM(B69:F69,H69)=0,"",SUM(B69:F69,H69))</f>
-        <v/>
-      </c>
-      <c r="J69" s="10" t="str">
+        <v>1401</v>
+      </c>
+      <c r="J69" s="10">
         <f t="shared" ref="J69:J132" si="3">IF(I69="","",1440-I69)</f>
-        <v/>
-      </c>
-      <c r="K69" s="11"/>
-      <c r="L69" s="11"/>
-      <c r="M69" s="11"/>
-      <c r="N69" s="12"/>
+        <v>39</v>
+      </c>
+      <c r="K69" s="11" t="s">
+        <v>60</v>
+      </c>
+      <c r="L69" s="11" t="s">
+        <v>67</v>
+      </c>
+      <c r="M69" s="11" t="s">
+        <v>63</v>
+      </c>
+      <c r="N69" s="12" t="s">
+        <v>127</v>
+      </c>
     </row>
     <row r="70" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A70" s="8"/>
-      <c r="B70" s="9"/>
-      <c r="C70" s="9"/>
-      <c r="D70" s="9"/>
-      <c r="E70" s="9"/>
-      <c r="F70" s="9"/>
-      <c r="G70" s="9"/>
-      <c r="H70" s="9"/>
-      <c r="I70" s="10" t="str">
+      <c r="A70" s="8">
+        <v>46314</v>
+      </c>
+      <c r="B70" s="9">
+        <v>615</v>
+      </c>
+      <c r="C70" s="9">
+        <v>0</v>
+      </c>
+      <c r="D70" s="9">
+        <v>53</v>
+      </c>
+      <c r="E70" s="9">
+        <v>0</v>
+      </c>
+      <c r="F70" s="9">
+        <v>0</v>
+      </c>
+      <c r="G70" s="9">
+        <v>0</v>
+      </c>
+      <c r="H70" s="9">
+        <v>655</v>
+      </c>
+      <c r="I70" s="10">
         <f t="shared" si="2"/>
-        <v/>
-      </c>
-      <c r="J70" s="10" t="str">
+        <v>1323</v>
+      </c>
+      <c r="J70" s="10">
         <f t="shared" si="3"/>
-        <v/>
-      </c>
-      <c r="K70" s="11"/>
-      <c r="L70" s="11"/>
-      <c r="M70" s="11"/>
-      <c r="N70" s="12"/>
+        <v>117</v>
+      </c>
+      <c r="K70" s="11" t="s">
+        <v>63</v>
+      </c>
+      <c r="L70" s="11" t="s">
+        <v>67</v>
+      </c>
+      <c r="M70" s="11" t="s">
+        <v>63</v>
+      </c>
+      <c r="N70" s="12" t="s">
+        <v>128</v>
+      </c>
     </row>
     <row r="71" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A71" s="8"/>
-      <c r="B71" s="9"/>
-      <c r="C71" s="9"/>
-      <c r="D71" s="9"/>
-      <c r="E71" s="9"/>
-      <c r="F71" s="9"/>
-      <c r="G71" s="9"/>
-      <c r="H71" s="9"/>
-      <c r="I71" s="10" t="str">
+      <c r="A71" s="8">
+        <v>46315</v>
+      </c>
+      <c r="B71" s="9">
+        <v>560</v>
+      </c>
+      <c r="C71" s="9">
+        <v>102</v>
+      </c>
+      <c r="D71" s="9">
+        <v>0</v>
+      </c>
+      <c r="E71" s="9">
+        <v>0</v>
+      </c>
+      <c r="F71" s="9">
+        <v>0</v>
+      </c>
+      <c r="G71" s="9">
+        <v>0</v>
+      </c>
+      <c r="H71" s="9">
+        <v>773</v>
+      </c>
+      <c r="I71" s="10">
         <f t="shared" si="2"/>
-        <v/>
-      </c>
-      <c r="J71" s="10" t="str">
+        <v>1435</v>
+      </c>
+      <c r="J71" s="10">
         <f t="shared" si="3"/>
-        <v/>
-      </c>
-      <c r="K71" s="11"/>
-      <c r="L71" s="11"/>
-      <c r="M71" s="11"/>
-      <c r="N71" s="12"/>
+        <v>5</v>
+      </c>
+      <c r="K71" s="11" t="s">
+        <v>63</v>
+      </c>
+      <c r="L71" s="11" t="s">
+        <v>67</v>
+      </c>
+      <c r="M71" s="11" t="s">
+        <v>63</v>
+      </c>
+      <c r="N71" s="12" t="s">
+        <v>129</v>
+      </c>
     </row>
     <row r="72" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A72" s="8"/>

--- a/12603996.xlsx
+++ b/12603996.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://lpuin-my.sharepoint.com/personal/shubham_bither2026_lpu_in/Documents/CAP776/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="875" documentId="8_{04F8DF2E-49C5-3B44-B164-C4F738DF63B4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{3233D9BD-7FFF-4F38-A1A5-C511A2A29D9D}"/>
+  <xr:revisionPtr revIDLastSave="913" documentId="8_{04F8DF2E-49C5-3B44-B164-C4F738DF63B4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{30BCC93B-46EE-4DEE-B00B-E82892549FA9}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13176" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="317" uniqueCount="130">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="329" uniqueCount="133">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -425,6 +425,15 @@
   </si>
   <si>
     <t>happy dusshera</t>
+  </si>
+  <si>
+    <t>restarted dsa</t>
+  </si>
+  <si>
+    <t>solved some dsa array questions</t>
+  </si>
+  <si>
+    <t>watched a movie, did rest,re-arrange room</t>
   </si>
 </sst>
 </file>
@@ -4222,70 +4231,142 @@
       </c>
     </row>
     <row r="72" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A72" s="8"/>
-      <c r="B72" s="9"/>
-      <c r="C72" s="9"/>
-      <c r="D72" s="9"/>
-      <c r="E72" s="9"/>
-      <c r="F72" s="9"/>
-      <c r="G72" s="9"/>
-      <c r="H72" s="9"/>
-      <c r="I72" s="10" t="str">
+      <c r="A72" s="8">
+        <v>46316</v>
+      </c>
+      <c r="B72" s="9">
+        <v>312</v>
+      </c>
+      <c r="C72" s="9">
+        <v>62</v>
+      </c>
+      <c r="D72" s="9">
+        <v>142</v>
+      </c>
+      <c r="E72" s="9">
+        <v>60</v>
+      </c>
+      <c r="F72" s="9">
+        <v>150</v>
+      </c>
+      <c r="G72" s="9">
+        <v>3</v>
+      </c>
+      <c r="H72" s="9">
+        <v>640</v>
+      </c>
+      <c r="I72" s="10">
         <f t="shared" si="2"/>
-        <v/>
-      </c>
-      <c r="J72" s="10" t="str">
+        <v>1366</v>
+      </c>
+      <c r="J72" s="10">
         <f t="shared" si="3"/>
-        <v/>
-      </c>
-      <c r="K72" s="11"/>
-      <c r="L72" s="11"/>
-      <c r="M72" s="11"/>
-      <c r="N72" s="12"/>
+        <v>74</v>
+      </c>
+      <c r="K72" s="11" t="s">
+        <v>66</v>
+      </c>
+      <c r="L72" s="11" t="s">
+        <v>61</v>
+      </c>
+      <c r="M72" s="11" t="s">
+        <v>63</v>
+      </c>
+      <c r="N72" s="12" t="s">
+        <v>130</v>
+      </c>
     </row>
     <row r="73" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A73" s="8"/>
-      <c r="B73" s="9"/>
-      <c r="C73" s="9"/>
-      <c r="D73" s="9"/>
-      <c r="E73" s="9"/>
-      <c r="F73" s="9"/>
-      <c r="G73" s="9"/>
-      <c r="H73" s="9"/>
-      <c r="I73" s="10" t="str">
+      <c r="A73" s="8">
+        <v>46317</v>
+      </c>
+      <c r="B73" s="9">
+        <v>291</v>
+      </c>
+      <c r="C73" s="9">
+        <v>132</v>
+      </c>
+      <c r="D73" s="9">
+        <v>122</v>
+      </c>
+      <c r="E73" s="9">
+        <v>36</v>
+      </c>
+      <c r="F73" s="9">
+        <v>300</v>
+      </c>
+      <c r="G73" s="9">
+        <v>6</v>
+      </c>
+      <c r="H73" s="9">
+        <v>550</v>
+      </c>
+      <c r="I73" s="10">
         <f t="shared" si="2"/>
-        <v/>
-      </c>
-      <c r="J73" s="10" t="str">
+        <v>1431</v>
+      </c>
+      <c r="J73" s="10">
         <f t="shared" si="3"/>
-        <v/>
-      </c>
-      <c r="K73" s="11"/>
-      <c r="L73" s="11"/>
-      <c r="M73" s="11"/>
-      <c r="N73" s="12"/>
-    </row>
-    <row r="74" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A74" s="8"/>
-      <c r="B74" s="9"/>
-      <c r="C74" s="9"/>
-      <c r="D74" s="9"/>
-      <c r="E74" s="9"/>
-      <c r="F74" s="9"/>
-      <c r="G74" s="9"/>
-      <c r="H74" s="9"/>
-      <c r="I74" s="10" t="str">
+        <v>9</v>
+      </c>
+      <c r="K73" s="11" t="s">
+        <v>63</v>
+      </c>
+      <c r="L73" s="11" t="s">
+        <v>60</v>
+      </c>
+      <c r="M73" s="11" t="s">
+        <v>63</v>
+      </c>
+      <c r="N73" s="12" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="74" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A74" s="8">
+        <v>46318</v>
+      </c>
+      <c r="B74" s="9">
+        <v>381</v>
+      </c>
+      <c r="C74" s="9">
+        <v>45</v>
+      </c>
+      <c r="D74" s="9">
+        <v>0</v>
+      </c>
+      <c r="E74" s="9">
+        <v>0</v>
+      </c>
+      <c r="F74" s="9">
+        <v>250</v>
+      </c>
+      <c r="G74" s="9">
+        <v>5</v>
+      </c>
+      <c r="H74" s="9">
+        <v>621</v>
+      </c>
+      <c r="I74" s="10">
         <f t="shared" si="2"/>
-        <v/>
-      </c>
-      <c r="J74" s="10" t="str">
+        <v>1297</v>
+      </c>
+      <c r="J74" s="10">
         <f t="shared" si="3"/>
-        <v/>
-      </c>
-      <c r="K74" s="11"/>
-      <c r="L74" s="11"/>
-      <c r="M74" s="11"/>
-      <c r="N74" s="12"/>
+        <v>143</v>
+      </c>
+      <c r="K74" s="11" t="s">
+        <v>63</v>
+      </c>
+      <c r="L74" s="11" t="s">
+        <v>67</v>
+      </c>
+      <c r="M74" s="11" t="s">
+        <v>63</v>
+      </c>
+      <c r="N74" s="12" t="s">
+        <v>132</v>
+      </c>
     </row>
     <row r="75" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A75" s="8"/>

--- a/12603996.xlsx
+++ b/12603996.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30430"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30527"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://lpuin-my.sharepoint.com/personal/shubham_bither2026_lpu_in/Documents/CAP776/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="913" documentId="8_{04F8DF2E-49C5-3B44-B164-C4F738DF63B4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{30BCC93B-46EE-4DEE-B00B-E82892549FA9}"/>
+  <xr:revisionPtr revIDLastSave="962" documentId="8_{04F8DF2E-49C5-3B44-B164-C4F738DF63B4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{AD841695-21D7-47EB-B001-1545B1E1AD0E}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13176" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="329" uniqueCount="133">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="345" uniqueCount="136">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -434,6 +434,15 @@
   </si>
   <si>
     <t>watched a movie, did rest,re-arrange room</t>
+  </si>
+  <si>
+    <t>bought new laptop for business</t>
+  </si>
+  <si>
+    <t>did new laptop setup</t>
+  </si>
+  <si>
+    <t>completed maths test</t>
   </si>
 </sst>
 </file>
@@ -4369,92 +4378,188 @@
       </c>
     </row>
     <row r="75" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A75" s="8"/>
-      <c r="B75" s="9"/>
-      <c r="C75" s="9"/>
-      <c r="D75" s="9"/>
-      <c r="E75" s="9"/>
-      <c r="F75" s="9"/>
-      <c r="G75" s="9"/>
-      <c r="H75" s="9"/>
-      <c r="I75" s="10" t="str">
+      <c r="A75" s="8">
+        <v>46319</v>
+      </c>
+      <c r="B75" s="9">
+        <v>516</v>
+      </c>
+      <c r="C75" s="9">
+        <v>45</v>
+      </c>
+      <c r="D75" s="9">
+        <v>32</v>
+      </c>
+      <c r="E75" s="9">
+        <v>120</v>
+      </c>
+      <c r="F75" s="9">
+        <v>0</v>
+      </c>
+      <c r="G75" s="9">
+        <v>0</v>
+      </c>
+      <c r="H75" s="9">
+        <v>722</v>
+      </c>
+      <c r="I75" s="10">
         <f t="shared" si="2"/>
-        <v/>
-      </c>
-      <c r="J75" s="10" t="str">
+        <v>1435</v>
+      </c>
+      <c r="J75" s="10">
         <f t="shared" si="3"/>
-        <v/>
-      </c>
-      <c r="K75" s="11"/>
-      <c r="L75" s="11"/>
-      <c r="M75" s="11"/>
-      <c r="N75" s="12"/>
+        <v>5</v>
+      </c>
+      <c r="K75" s="11" t="s">
+        <v>60</v>
+      </c>
+      <c r="L75" s="11" t="s">
+        <v>60</v>
+      </c>
+      <c r="M75" s="11" t="s">
+        <v>63</v>
+      </c>
+      <c r="N75" s="12" t="s">
+        <v>133</v>
+      </c>
     </row>
     <row r="76" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A76" s="8"/>
-      <c r="B76" s="9"/>
-      <c r="C76" s="9"/>
-      <c r="D76" s="9"/>
-      <c r="E76" s="9"/>
-      <c r="F76" s="9"/>
-      <c r="G76" s="9"/>
-      <c r="H76" s="9"/>
-      <c r="I76" s="10" t="str">
+      <c r="A76" s="8">
+        <v>46320</v>
+      </c>
+      <c r="B76" s="9">
+        <v>516</v>
+      </c>
+      <c r="C76" s="9">
+        <v>0</v>
+      </c>
+      <c r="D76" s="9">
+        <v>92</v>
+      </c>
+      <c r="E76" s="9">
+        <v>0</v>
+      </c>
+      <c r="F76" s="9">
+        <v>0</v>
+      </c>
+      <c r="G76" s="9">
+        <v>0</v>
+      </c>
+      <c r="H76" s="9">
+        <v>755</v>
+      </c>
+      <c r="I76" s="10">
         <f t="shared" si="2"/>
-        <v/>
-      </c>
-      <c r="J76" s="10" t="str">
+        <v>1363</v>
+      </c>
+      <c r="J76" s="10">
         <f t="shared" si="3"/>
-        <v/>
-      </c>
-      <c r="K76" s="11"/>
-      <c r="L76" s="11"/>
-      <c r="M76" s="11"/>
-      <c r="N76" s="12"/>
+        <v>77</v>
+      </c>
+      <c r="K76" s="11" t="s">
+        <v>60</v>
+      </c>
+      <c r="L76" s="11" t="s">
+        <v>61</v>
+      </c>
+      <c r="M76" s="11" t="s">
+        <v>63</v>
+      </c>
+      <c r="N76" s="12" t="s">
+        <v>134</v>
+      </c>
     </row>
     <row r="77" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A77" s="8"/>
-      <c r="B77" s="9"/>
-      <c r="C77" s="9"/>
-      <c r="D77" s="9"/>
-      <c r="E77" s="9"/>
-      <c r="F77" s="9"/>
-      <c r="G77" s="9"/>
-      <c r="H77" s="9"/>
-      <c r="I77" s="10" t="str">
+      <c r="A77" s="8">
+        <v>46321</v>
+      </c>
+      <c r="B77" s="9">
+        <v>372</v>
+      </c>
+      <c r="C77" s="9">
+        <v>83</v>
+      </c>
+      <c r="D77" s="9">
+        <v>240</v>
+      </c>
+      <c r="E77" s="9">
+        <v>0</v>
+      </c>
+      <c r="F77" s="9">
+        <v>0</v>
+      </c>
+      <c r="G77" s="9">
+        <v>0</v>
+      </c>
+      <c r="H77" s="9">
+        <v>653</v>
+      </c>
+      <c r="I77" s="10">
         <f t="shared" si="2"/>
-        <v/>
-      </c>
-      <c r="J77" s="10" t="str">
+        <v>1348</v>
+      </c>
+      <c r="J77" s="10">
         <f t="shared" si="3"/>
-        <v/>
-      </c>
-      <c r="K77" s="11"/>
-      <c r="L77" s="11"/>
-      <c r="M77" s="11"/>
-      <c r="N77" s="12"/>
+        <v>92</v>
+      </c>
+      <c r="K77" s="11" t="s">
+        <v>60</v>
+      </c>
+      <c r="L77" s="11" t="s">
+        <v>61</v>
+      </c>
+      <c r="M77" s="11" t="s">
+        <v>63</v>
+      </c>
+      <c r="N77" s="12" t="s">
+        <v>135</v>
+      </c>
     </row>
     <row r="78" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A78" s="8"/>
-      <c r="B78" s="9"/>
-      <c r="C78" s="9"/>
-      <c r="D78" s="9"/>
-      <c r="E78" s="9"/>
-      <c r="F78" s="9"/>
-      <c r="G78" s="9"/>
-      <c r="H78" s="9"/>
-      <c r="I78" s="10" t="str">
+      <c r="A78" s="8">
+        <v>46322</v>
+      </c>
+      <c r="B78" s="9">
+        <v>362</v>
+      </c>
+      <c r="C78" s="9">
+        <v>122</v>
+      </c>
+      <c r="D78" s="9">
+        <v>120</v>
+      </c>
+      <c r="E78" s="9">
+        <v>0</v>
+      </c>
+      <c r="F78" s="9">
+        <v>250</v>
+      </c>
+      <c r="G78" s="9">
+        <v>5</v>
+      </c>
+      <c r="H78" s="9">
+        <v>520</v>
+      </c>
+      <c r="I78" s="10">
         <f t="shared" si="2"/>
-        <v/>
-      </c>
-      <c r="J78" s="10" t="str">
+        <v>1374</v>
+      </c>
+      <c r="J78" s="10">
         <f t="shared" si="3"/>
-        <v/>
-      </c>
-      <c r="K78" s="11"/>
-      <c r="L78" s="11"/>
-      <c r="M78" s="11"/>
-      <c r="N78" s="12"/>
+        <v>66</v>
+      </c>
+      <c r="K78" s="11" t="s">
+        <v>66</v>
+      </c>
+      <c r="L78" s="11" t="s">
+        <v>61</v>
+      </c>
+      <c r="M78" s="11" t="s">
+        <v>51</v>
+      </c>
+      <c r="N78" s="12" t="s">
+        <v>68</v>
+      </c>
     </row>
     <row r="79" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A79" s="8"/>

--- a/12603996.xlsx
+++ b/12603996.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://lpuin-my.sharepoint.com/personal/shubham_bither2026_lpu_in/Documents/CAP776/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="962" documentId="8_{04F8DF2E-49C5-3B44-B164-C4F738DF63B4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{AD841695-21D7-47EB-B001-1545B1E1AD0E}"/>
+  <xr:revisionPtr revIDLastSave="998" documentId="8_{04F8DF2E-49C5-3B44-B164-C4F738DF63B4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{CEC7639B-FFD0-4C70-BBB5-94C100A5A163}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13176" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="345" uniqueCount="136">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="357" uniqueCount="138">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -443,6 +443,12 @@
   </si>
   <si>
     <t>completed maths test</t>
+  </si>
+  <si>
+    <t>prepared for ca2 of networking</t>
+  </si>
+  <si>
+    <t>went to home ,did c++ project preparation</t>
   </si>
 </sst>
 </file>
@@ -4562,70 +4568,138 @@
       </c>
     </row>
     <row r="79" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A79" s="8"/>
-      <c r="B79" s="9"/>
-      <c r="C79" s="9"/>
-      <c r="D79" s="9"/>
-      <c r="E79" s="9"/>
-      <c r="F79" s="9"/>
-      <c r="G79" s="9"/>
-      <c r="H79" s="9"/>
-      <c r="I79" s="10" t="str">
+      <c r="A79" s="8">
+        <v>46323</v>
+      </c>
+      <c r="B79" s="9">
+        <v>332</v>
+      </c>
+      <c r="C79" s="9">
+        <v>152</v>
+      </c>
+      <c r="D79" s="9">
+        <v>180</v>
+      </c>
+      <c r="E79" s="9">
+        <v>0</v>
+      </c>
+      <c r="F79" s="9">
+        <v>150</v>
+      </c>
+      <c r="G79" s="9">
+        <v>3</v>
+      </c>
+      <c r="H79" s="9">
+        <v>561</v>
+      </c>
+      <c r="I79" s="10">
         <f t="shared" si="2"/>
-        <v/>
-      </c>
-      <c r="J79" s="10" t="str">
+        <v>1375</v>
+      </c>
+      <c r="J79" s="10">
         <f t="shared" si="3"/>
-        <v/>
-      </c>
-      <c r="K79" s="11"/>
-      <c r="L79" s="11"/>
-      <c r="M79" s="11"/>
-      <c r="N79" s="12"/>
+        <v>65</v>
+      </c>
+      <c r="K79" s="11" t="s">
+        <v>66</v>
+      </c>
+      <c r="L79" s="11" t="s">
+        <v>61</v>
+      </c>
+      <c r="M79" s="11" t="s">
+        <v>51</v>
+      </c>
+      <c r="N79" s="12" t="s">
+        <v>136</v>
+      </c>
     </row>
     <row r="80" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A80" s="8"/>
-      <c r="B80" s="9"/>
-      <c r="C80" s="9"/>
-      <c r="D80" s="9"/>
-      <c r="E80" s="9"/>
-      <c r="F80" s="9"/>
-      <c r="G80" s="9"/>
-      <c r="H80" s="9"/>
-      <c r="I80" s="10" t="str">
+      <c r="A80" s="8">
+        <v>46324</v>
+      </c>
+      <c r="B80" s="9">
+        <v>332</v>
+      </c>
+      <c r="C80" s="9">
+        <v>89</v>
+      </c>
+      <c r="D80" s="9">
+        <v>240</v>
+      </c>
+      <c r="E80" s="9">
+        <v>0</v>
+      </c>
+      <c r="F80" s="9">
+        <v>250</v>
+      </c>
+      <c r="G80" s="9">
+        <v>5</v>
+      </c>
+      <c r="H80" s="9">
+        <v>529</v>
+      </c>
+      <c r="I80" s="10">
         <f t="shared" si="2"/>
-        <v/>
-      </c>
-      <c r="J80" s="10" t="str">
+        <v>1440</v>
+      </c>
+      <c r="J80" s="10">
         <f t="shared" si="3"/>
-        <v/>
-      </c>
-      <c r="K80" s="11"/>
-      <c r="L80" s="11"/>
-      <c r="M80" s="11"/>
-      <c r="N80" s="12"/>
-    </row>
-    <row r="81" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A81" s="8"/>
-      <c r="B81" s="9"/>
-      <c r="C81" s="9"/>
-      <c r="D81" s="9"/>
+        <v>0</v>
+      </c>
+      <c r="K80" s="11" t="s">
+        <v>63</v>
+      </c>
+      <c r="L80" s="11" t="s">
+        <v>67</v>
+      </c>
+      <c r="M80" s="11" t="s">
+        <v>63</v>
+      </c>
+      <c r="N80" s="12" t="s">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="81" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A81" s="8">
+        <v>46325</v>
+      </c>
+      <c r="B81" s="9">
+        <v>332</v>
+      </c>
+      <c r="C81" s="9">
+        <v>132</v>
+      </c>
+      <c r="D81" s="9">
+        <v>82</v>
+      </c>
       <c r="E81" s="9"/>
-      <c r="F81" s="9"/>
-      <c r="G81" s="9"/>
+      <c r="F81" s="9">
+        <v>250</v>
+      </c>
+      <c r="G81" s="9">
+        <v>5</v>
+      </c>
       <c r="H81" s="9"/>
-      <c r="I81" s="10" t="str">
+      <c r="I81" s="10">
         <f t="shared" si="2"/>
-        <v/>
-      </c>
-      <c r="J81" s="10" t="str">
+        <v>796</v>
+      </c>
+      <c r="J81" s="10">
         <f t="shared" si="3"/>
-        <v/>
-      </c>
-      <c r="K81" s="11"/>
-      <c r="L81" s="11"/>
-      <c r="M81" s="11"/>
-      <c r="N81" s="12"/>
+        <v>644</v>
+      </c>
+      <c r="K81" s="11" t="s">
+        <v>60</v>
+      </c>
+      <c r="L81" s="11" t="s">
+        <v>60</v>
+      </c>
+      <c r="M81" s="11" t="s">
+        <v>63</v>
+      </c>
+      <c r="N81" s="12" t="s">
+        <v>137</v>
+      </c>
     </row>
     <row r="82" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A82" s="8"/>
